--- a/tests/fixtures/22_weekly_timesheet/22_weekly_timesheet_pattern-from-draft.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/22_weekly_timesheet_pattern-from-draft.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -461,48 +461,41 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>col_day</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Day of week</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -512,7 +505,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>col_time_in</t>
+          <t>col_day</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -522,7 +515,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Time in</t>
+          <t>Day of week</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
@@ -536,7 +529,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>col_breaks</t>
+          <t>col_time_in</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -546,7 +539,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Breaks\n\(minutes\)</t>
+          <t>Time in</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -560,7 +553,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>col_time_out</t>
+          <t>col_breaks</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -570,35 +563,35 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Time out</t>
+          <t>Breaks\n\(minutes\)</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>company.name</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>col_time_out</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Time out</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -608,7 +601,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>employee.name</t>
+          <t>company.name</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -632,7 +625,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>employee.manager</t>
+          <t>employee.name</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -656,15 +649,19 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>employee.week_starting</t>
+          <t>employee.manager</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
     </row>
@@ -676,12 +673,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>week.day</t>
+          <t>employee.week_starting</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr"/>
@@ -696,12 +693,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>week.time_in</t>
+          <t>week.day</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -716,19 +713,15 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>week.breaks</t>
+          <t>week.time_in</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>\d+</t>
-        </is>
-      </c>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
     </row>
@@ -740,15 +733,19 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>week.time_out</t>
+          <t>week.breaks</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
     </row>
@@ -760,19 +757,15 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>rate.regular</t>
+          <t>week.time_out</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
     </row>
@@ -784,7 +777,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>rate.overtime</t>
+          <t>rate.regular</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -808,7 +801,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>rate.sick</t>
+          <t>rate.overtime</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -832,7 +825,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>rate.holiday</t>
+          <t>rate.sick</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -856,7 +849,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>rate.vacation</t>
+          <t>rate.holiday</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -880,7 +873,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>pay.regular</t>
+          <t>rate.vacation</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -904,7 +897,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>pay.overtime</t>
+          <t>pay.regular</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -928,7 +921,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>pay.sick</t>
+          <t>pay.overtime</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -952,7 +945,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>pay.holiday</t>
+          <t>pay.sick</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -976,7 +969,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>pay.vacation</t>
+          <t>pay.holiday</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1000,7 +993,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>pay.grand_total</t>
+          <t>pay.vacation</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1017,42 +1010,50 @@
       <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>pay.grand_total</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>cell:G2</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>company.name</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>cell:I4</t>
+          <t>cell:G2</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>employee.name</t>
+          <t>company.name</t>
         </is>
       </c>
       <c r="C27" s="5" t="n"/>
@@ -1063,12 +1064,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>cell:I5</t>
+          <t>cell:I4</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>employee.manager</t>
+          <t>employee.name</t>
         </is>
       </c>
       <c r="C28" s="5" t="n"/>
@@ -1079,12 +1080,12 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>cell:I6</t>
+          <t>cell:I5</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>employee.week_starting</t>
+          <t>employee.manager</t>
         </is>
       </c>
       <c r="C29" s="5" t="n"/>
@@ -1093,98 +1094,98 @@
       <c r="F29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>cell:I6</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>employee.week_starting</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>col_day</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>col_time_in</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>col_breaks</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>col_time_out</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>DATA:8</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>week.day</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>week.time_in</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>week.breaks</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>week.time_out</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>cell:H30</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>rate.regular</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>cell:I30</t>
+          <t>cell:H30</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>rate.overtime</t>
+          <t>rate.regular</t>
         </is>
       </c>
       <c r="C34" s="5" t="n"/>
@@ -1195,12 +1196,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>cell:J30</t>
+          <t>cell:I30</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>rate.sick</t>
+          <t>rate.overtime</t>
         </is>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -1211,12 +1212,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>cell:K30</t>
+          <t>cell:J30</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>rate.holiday</t>
+          <t>rate.sick</t>
         </is>
       </c>
       <c r="C36" s="5" t="n"/>
@@ -1227,12 +1228,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>cell:L30</t>
+          <t>cell:K30</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>rate.vacation</t>
+          <t>rate.holiday</t>
         </is>
       </c>
       <c r="C37" s="5" t="n"/>
@@ -1243,12 +1244,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>cell:H31</t>
+          <t>cell:L30</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>pay.regular</t>
+          <t>rate.vacation</t>
         </is>
       </c>
       <c r="C38" s="5" t="n"/>
@@ -1259,12 +1260,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>cell:I31</t>
+          <t>cell:H31</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>pay.overtime</t>
+          <t>pay.regular</t>
         </is>
       </c>
       <c r="C39" s="5" t="n"/>
@@ -1275,12 +1276,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>cell:J31</t>
+          <t>cell:I31</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>pay.sick</t>
+          <t>pay.overtime</t>
         </is>
       </c>
       <c r="C40" s="5" t="n"/>
@@ -1291,12 +1292,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>cell:K31</t>
+          <t>cell:J31</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>pay.holiday</t>
+          <t>pay.sick</t>
         </is>
       </c>
       <c r="C41" s="5" t="n"/>
@@ -1307,12 +1308,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>cell:L31</t>
+          <t>cell:K31</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>pay.vacation</t>
+          <t>pay.holiday</t>
         </is>
       </c>
       <c r="C42" s="5" t="n"/>
@@ -1323,12 +1324,12 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>cell:K33</t>
+          <t>cell:L31</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>pay.grand_total</t>
+          <t>pay.vacation</t>
         </is>
       </c>
       <c r="C43" s="5" t="n"/>
@@ -1337,16 +1338,32 @@
       <c r="F43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>cell:K33</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>pay.grand_total</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
